--- a/sampleprojects/CorporateTax/excel/states/IA_corp.xlsx
+++ b/sampleprojects/CorporateTax/excel/states/IA_corp.xlsx
@@ -70,7 +70,7 @@
     <t>Meets economic nexus threshold ($100K gross receipts); result.ia_gross_receipts is greater than or equal to result.ia_economic_nexus_threshold</t>
   </si>
   <si>
-    <t>result.ia_gross_receipts &gt;= result.ia_economic_nexus_threshold</t>
+    <t>ia_result.gross_receipts &gt;= ia_result.economic_nexus_threshold</t>
   </si>
   <si>
     <t>-</t>
@@ -85,7 +85,7 @@
     <t>Physical nexus - filing required</t>
   </si>
   <si>
-    <t>set result.ia_has_nexus = true;</t>
+    <t>set ia_result.has_nexus = true;</t>
   </si>
   <si>
     <t>X</t>
@@ -97,7 +97,7 @@
     <t>No nexus - no filing required</t>
   </si>
   <si>
-    <t>set result.ia_has_nexus = false; set result.ia_tax_liability = 0.0;</t>
+    <t>set ia_result.has_nexus = false; set ia_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate IA Income Adjustments</t>
@@ -115,19 +115,19 @@
     <t>Has Iowa nexus</t>
   </si>
   <si>
-    <t>result.ia_has_nexus is equal to true</t>
+    <t>ia_result.has_nexus is equal to true</t>
   </si>
   <si>
     <t>Calculate Iowa state additions and subtractions; Calculate state-specific income adjustments</t>
   </si>
   <si>
-    <t>set result.ia_state_additions = 0.0; if result.ia_state_taxes_deducted != 0.0 then set result.ia_state_additions = result.ia_state_additions + result.ia_state_taxes_deducted; endif set result.ia_state_subtractions = 0.0; if result.ia_us_interest_income != 0.0 then set result.ia_state_subtractions = result.ia_state_subtractions + result.ia_us_interest_income; endif if result.ia_municipal_interest != 0.0 then set result.ia_state_subtractions = result.ia_state_subtractions + result.ia_municipal_interest; endif add (("Iowa additions: $" + string value of (result.ia_state_additions)) + ", subtractions: $") + string value of (result.ia_state_subtractions) to job.audit_trail;</t>
+    <t>set ia_result.state_additions = 0.0; if ia_result.state_taxes_deducted != 0.0 then set ia_result.state_additions = ia_result.state_additions + ia_result.state_taxes_deducted; endif set ia_result.state_subtractions = 0.0; if ia_result.us_interest_income != 0.0 then set ia_result.state_subtractions = ia_result.state_subtractions + ia_result.us_interest_income; endif if ia_result.municipal_interest != 0.0 then set ia_result.state_subtractions = ia_result.state_subtractions + ia_result.municipal_interest; endif add (("Iowa additions: $" + string value of (ia_result.state_additions)) + ", subtractions: $") + string value of (ia_result.state_subtractions) to job.audit_trail;</t>
   </si>
   <si>
     <t>No nexus - no adjustments</t>
   </si>
   <si>
-    <t>set result.ia_state_additions = 0.0; set result.ia_state_subtractions = 0.0;</t>
+    <t>set ia_result.state_additions = 0.0; set ia_result.state_subtractions = 0.0;</t>
   </si>
   <si>
     <t>DT: Calculate IA State Tax</t>
@@ -145,31 +145,31 @@
     <t>Has positive taxable income; result.ia_apportioned_income is greater than 0</t>
   </si>
   <si>
-    <t>result.ia_apportioned_income &gt; 0.0</t>
+    <t>ia_result.apportioned_income &gt; 0.0</t>
   </si>
   <si>
     <t>Income exceeds $100,000 bracket threshold; result.ia_taxable_income is greater than result.ia_tax_bracket_threshold</t>
   </si>
   <si>
-    <t>result.ia_taxable_income &gt; result.ia_tax_bracket_threshold</t>
+    <t>ia_result.taxable_income &gt; ia_result.tax_bracket_threshold</t>
   </si>
   <si>
     <t>Calculate Iowa tax with graduated rates - income over $100K; Apply graduated rates: 5.5% on first $100K, 7.1% on excess</t>
   </si>
   <si>
-    <t>set result.ia_taxable_income = the maximum of (result.ia_apportioned_income + result.ia_state_additions - result.ia_state_subtractions) and (0.0); set result.ia_tax_bracket_1 = result.ia_tax_bracket_threshold * result.ia_corp_tax_rate_bracket_1; set result.ia_tax_bracket_2 = (result.ia_taxable_income - result.ia_tax_bracket_threshold) * result.ia_corp_tax_rate_bracket_2; set result.ia_tax_liability = the maximum of (result.ia_tax_bracket_1 + result.ia_tax_bracket_2 - result.ia_state_credits) and (0.0); set result.ia_refund_or_owed = result.ia_estimated_payments - result.ia_tax_liability; add "Iowa taxable income: $" + string value of (result.ia_taxable_income) to job.audit_trail; add "Iowa tax bracket 1 (5.5% on $100K): $" + string value of (result.ia_tax_bracket_1) to job.audit_trail; add "Iowa tax bracket 2 (7.1% on excess): $" + string value of (result.ia_tax_bracket_2) to job.audit_trail; add "Iowa tax liability: $" + string value of (result.ia_tax_liability) to job.audit_trail;</t>
+    <t>set ia_result.taxable_income = the maximum of (ia_result.apportioned_income + ia_result.state_additions - ia_result.state_subtractions) and (0.0); set ia_result.tax_bracket_1 = ia_result.tax_bracket_threshold * ia_result.corp_tax_rate_bracket_1; set ia_result.tax_bracket_2 = (ia_result.taxable_income - ia_result.tax_bracket_threshold) * ia_result.corp_tax_rate_bracket_2; set ia_result.tax_liability = the maximum of (ia_result.tax_bracket_1 + ia_result.tax_bracket_2 - ia_result.state_credits) and (0.0); set ia_result.refund_or_owed = ia_result.estimated_payments - ia_result.tax_liability; add "Iowa taxable income: $" + string value of (ia_result.taxable_income) to job.audit_trail; add "Iowa tax bracket 1 (5.5% on $100K): $" + string value of (ia_result.tax_bracket_1) to job.audit_trail; add "Iowa tax bracket 2 (7.1% on excess): $" + string value of (ia_result.tax_bracket_2) to job.audit_trail; add "Iowa tax liability: $" + string value of (ia_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>Calculate Iowa tax - income $100K or less (only 5.5% rate); Apply only 5.5% rate for income under $100K</t>
   </si>
   <si>
-    <t>set result.ia_taxable_income = the maximum of (result.ia_apportioned_income + result.ia_state_additions - result.ia_state_subtractions) and (0.0); set result.ia_tax_bracket_1 = result.ia_taxable_income * result.ia_corp_tax_rate_bracket_1; set result.ia_tax_bracket_2 = 0.0; set result.ia_tax_liability = the maximum of (result.ia_tax_bracket_1 - result.ia_state_credits) and (0.0); set result.ia_refund_or_owed = result.ia_estimated_payments - result.ia_tax_liability; add "Iowa taxable income: $" + string value of (result.ia_taxable_income) to job.audit_trail; add "Iowa tax liability (5.5%): $" + string value of (result.ia_tax_liability) to job.audit_trail;</t>
+    <t>set ia_result.taxable_income = the maximum of (ia_result.apportioned_income + ia_result.state_additions - ia_result.state_subtractions) and (0.0); set ia_result.tax_bracket_1 = ia_result.taxable_income * ia_result.corp_tax_rate_bracket_1; set ia_result.tax_bracket_2 = 0.0; set ia_result.tax_liability = the maximum of (ia_result.tax_bracket_1 - ia_result.state_credits) and (0.0); set ia_result.refund_or_owed = ia_result.estimated_payments - ia_result.tax_liability; add "Iowa taxable income: $" + string value of (ia_result.taxable_income) to job.audit_trail; add "Iowa tax liability (5.5%): $" + string value of (ia_result.tax_liability) to job.audit_trail;</t>
   </si>
   <si>
     <t>No taxable income - no tax liability</t>
   </si>
   <si>
-    <t>set result.ia_taxable_income = 0.0; set result.ia_tax_liability = 0.0;</t>
+    <t>set ia_result.taxable_income = 0.0; set ia_result.tax_liability = 0.0;</t>
   </si>
   <si>
     <t>No nexus - no tax liability</t>
@@ -217,13 +217,13 @@
     <t>Reference</t>
   </si>
   <si>
-    <t>result</t>
+    <t>ia_result</t>
   </si>
   <si>
     <t>(21 attributes)</t>
   </si>
   <si>
-    <t>ia_apportioned_income</t>
+    <t>apportioned_income</t>
   </si>
   <si>
     <t>double</t>
@@ -238,7 +238,7 @@
     <t>Declared from decision-table usage; referenced by IA but never declared (campaign #948 Phase 1)</t>
   </si>
   <si>
-    <t>ia_apportionment_formula</t>
+    <t>apportionment_formula</t>
   </si>
   <si>
     <t>string</t>
@@ -250,7 +250,7 @@
     <t>IA uses single-sales factor apportionment (100% sales)</t>
   </si>
   <si>
-    <t>ia_corp_tax_rate_bracket_1</t>
+    <t>corp_tax_rate_bracket_1</t>
   </si>
   <si>
     <t>0.055</t>
@@ -259,7 +259,7 @@
     <t>IA corporate income tax rate bracket 1: 5.5% on income up to $100,000 (Iowa Code § 422.33)</t>
   </si>
   <si>
-    <t>ia_corp_tax_rate_bracket_2</t>
+    <t>corp_tax_rate_bracket_2</t>
   </si>
   <si>
     <t>0.071</t>
@@ -268,7 +268,7 @@
     <t>IA corporate income tax rate bracket 2: 7.1% on income over $100,000 (Iowa Code § 422.33)</t>
   </si>
   <si>
-    <t>ia_economic_nexus_threshold</t>
+    <t>economic_nexus_threshold</t>
   </si>
   <si>
     <t>100000.0</t>
@@ -277,13 +277,13 @@
     <t>IA economic nexus gross receipts threshold: $100,000</t>
   </si>
   <si>
-    <t>ia_estimated_payments</t>
-  </si>
-  <si>
-    <t>ia_gross_receipts</t>
-  </si>
-  <si>
-    <t>ia_has_nexus</t>
+    <t>estimated_payments</t>
+  </si>
+  <si>
+    <t>gross_receipts</t>
+  </si>
+  <si>
+    <t>has_nexus</t>
   </si>
   <si>
     <t>boolean</t>
@@ -295,64 +295,64 @@
     <t>Whether corporation has nexus with Iowa</t>
   </si>
   <si>
-    <t>ia_municipal_interest</t>
-  </si>
-  <si>
-    <t>ia_refund_or_owed</t>
-  </si>
-  <si>
-    <t>ia_state_additions</t>
+    <t>municipal_interest</t>
+  </si>
+  <si>
+    <t>refund_or_owed</t>
+  </si>
+  <si>
+    <t>state_additions</t>
   </si>
   <si>
     <t>IA additions to federal taxable income (state income taxes deducted federally, certain expenses, etc.)</t>
   </si>
   <si>
-    <t>ia_state_credits</t>
+    <t>state_credits</t>
   </si>
   <si>
     <t>IA tax credits (research activities, high quality jobs, renewable energy, historic preservation, etc.)</t>
   </si>
   <si>
-    <t>ia_state_subtractions</t>
+    <t>state_subtractions</t>
   </si>
   <si>
     <t>IA subtractions from federal taxable income (federal interest income, IA municipal bond interest, state NOL, etc.)</t>
   </si>
   <si>
-    <t>ia_state_taxes_deducted</t>
-  </si>
-  <si>
-    <t>ia_tax_bracket_1</t>
+    <t>state_taxes_deducted</t>
+  </si>
+  <si>
+    <t>tax_bracket_1</t>
   </si>
   <si>
     <t>IA tax on first $100,000 at 5.5%</t>
   </si>
   <si>
-    <t>ia_tax_bracket_2</t>
+    <t>tax_bracket_2</t>
   </si>
   <si>
     <t>IA tax on income over $100,000 at 7.1%</t>
   </si>
   <si>
-    <t>ia_tax_bracket_threshold</t>
+    <t>tax_bracket_threshold</t>
   </si>
   <si>
     <t>IA tax bracket threshold: $100,000</t>
   </si>
   <si>
-    <t>ia_tax_liability</t>
+    <t>tax_liability</t>
   </si>
   <si>
     <t>IA corporate income tax liability</t>
   </si>
   <si>
-    <t>ia_taxable_income</t>
+    <t>taxable_income</t>
   </si>
   <si>
     <t>IA taxable income after apportionment and modifications</t>
   </si>
   <si>
-    <t>ia_transaction_threshold</t>
+    <t>transaction_threshold</t>
   </si>
   <si>
     <t>integer</t>
@@ -364,7 +364,7 @@
     <t>IA eliminated transaction count threshold as of 7/1/2023</t>
   </si>
   <si>
-    <t>ia_us_interest_income</t>
+    <t>us_interest_income</t>
   </si>
 </sst>
 </file>
